--- a/evolution/word_usage_summary.xlsx
+++ b/evolution/word_usage_summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">2020s</t>
   </si>
   <si>
-    <t xml:space="preserve">All_Count</t>
+    <t xml:space="preserve">All words</t>
   </si>
   <si>
     <t xml:space="preserve">1913</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">223060</t>
   </si>
   <si>
-    <t xml:space="preserve">Reused_Count</t>
+    <t xml:space="preserve">Reused words</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">211228</t>
   </si>
   <si>
-    <t xml:space="preserve">New_Count</t>
+    <t xml:space="preserve">New words</t>
   </si>
   <si>
     <t xml:space="preserve">1886</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">11832</t>
   </si>
   <si>
-    <t xml:space="preserve">Topic_Count</t>
+    <t xml:space="preserve">Topic</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
@@ -108,16 +108,97 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
+    <t xml:space="preserve">Top 10 reused words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, subjects, children, training, design, treatment, generalization, baseline, behavioral, self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, study, design, treatment, results, children, self, training, social, effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">children, study, design, behavior, treatment, results, video, participants, training, effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention, study, design, children, participants, results, students, video, based, training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention, study, design, participants, children, training, students, skills, asd, based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 10 new words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, children, self, training, baseline, assessment, design, sensory, treatment, use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">performance, community, treatments, coaching, restraint, cognitive, conditions, improvement, casts, handicapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autism, matching, delay, developmental, object, participant, injury, spelling, second, output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">symbol, pecs, asd, stories, knee, protocol, seating, spectrum, slot, blending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ipad, 2016, tablet, gbg, fidelity, app, 2014, scribe, id, tau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">covid, pandemic, nick, 2020, asynchronous, compassion, 2021, hallucinations, emt, 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.95</t>
+  </si>
+  <si>
     <t xml:space="preserve">Min</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median</t>
+    <t xml:space="preserve">25th pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50th pct</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -126,28 +207,7 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3</t>
+    <t xml:space="preserve">75th pct</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
@@ -217,9 +277,6 @@
   </si>
   <si>
     <t xml:space="preserve">292.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topic</t>
   </si>
   <si>
     <t xml:space="preserve">Decade</t>
@@ -700,166 +757,164 @@
       <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
@@ -868,16 +923,85 @@
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -893,24 +1017,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -927,7 +1051,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -944,7 +1068,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -961,7 +1085,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -978,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -995,7 +1119,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -1012,7 +1136,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -1029,7 +1153,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -1046,7 +1170,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1063,7 +1187,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -1080,7 +1204,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -1097,7 +1221,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -1114,7 +1238,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1131,7 +1255,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -1148,7 +1272,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -1250,7 +1374,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
@@ -1267,7 +1391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -1284,7 +1408,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -1301,7 +1425,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
@@ -1318,7 +1442,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -1335,7 +1459,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
@@ -1352,7 +1476,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -1369,7 +1493,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
@@ -1386,7 +1510,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
@@ -1403,7 +1527,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
@@ -1505,7 +1629,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
@@ -1522,7 +1646,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
@@ -1539,7 +1663,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
@@ -1556,7 +1680,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -1573,7 +1697,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
@@ -1590,7 +1714,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -1607,7 +1731,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
@@ -1624,7 +1748,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
         <v>2</v>
@@ -1641,7 +1765,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -1658,7 +1782,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
@@ -1675,7 +1799,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -1692,7 +1816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
         <v>6</v>
@@ -1709,7 +1833,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
@@ -1726,7 +1850,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
         <v>2</v>
@@ -1743,7 +1867,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
@@ -1760,7 +1884,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
@@ -1777,7 +1901,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
@@ -1794,7 +1918,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
@@ -1811,7 +1935,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
         <v>1</v>
@@ -1828,7 +1952,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -1845,7 +1969,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
@@ -1862,7 +1986,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
@@ -1879,7 +2003,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>5</v>
@@ -1896,7 +2020,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
@@ -1913,7 +2037,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
         <v>1</v>
@@ -1930,7 +2054,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
         <v>3</v>
@@ -1947,7 +2071,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
@@ -1964,7 +2088,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
@@ -1981,7 +2105,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
         <v>6</v>
@@ -1998,7 +2122,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
@@ -2015,7 +2139,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
         <v>3</v>
@@ -2032,7 +2156,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
@@ -2049,7 +2173,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
@@ -2066,7 +2190,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
@@ -2083,7 +2207,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B71" t="s">
         <v>1</v>
@@ -2100,7 +2224,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -2117,7 +2241,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B73" t="s">
         <v>3</v>
@@ -2134,7 +2258,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
@@ -2151,7 +2275,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B75" t="s">
         <v>5</v>
@@ -2168,7 +2292,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>

--- a/evolution/word_usage_summary.xlsx
+++ b/evolution/word_usage_summary.xlsx
@@ -39,22 +39,22 @@
     <t xml:space="preserve">All words</t>
   </si>
   <si>
-    <t xml:space="preserve">1913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223060</t>
+    <t xml:space="preserve">2149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228642</t>
   </si>
   <si>
     <t xml:space="preserve">Reused words</t>
@@ -63,163 +63,166 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">2537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211228</t>
+    <t xml:space="preserve">2649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216487</t>
   </si>
   <si>
     <t xml:space="preserve">New words</t>
   </si>
   <si>
-    <t xml:space="preserve">1886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11832</t>
+    <t xml:space="preserve">1900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12155</t>
   </si>
   <si>
     <t xml:space="preserve">Topic</t>
   </si>
   <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 10 reused words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, subjects, children, design, training, behavioral, treatment, generalization, baseline, self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, study, design, treatment, results, children, self, training, social, effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">children, design, study, behavior, treatment, results, video, participants, training, effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study, intervention, design, children, participants, results, students, based, video, training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study, intervention, design, participants, children, training, students, based, skills, research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 10 new words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">behavior, self, children, training, ss, treatment, procedures, baseline, assessment, behavioral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">performance, community, treatments, coaching, restraint, cognitive, conditions, casts, handicapped, improve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autism, matching, delay, developmental, object, injury, participant, spelling, reduced, second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">symbol, pecs, asd, stories, knee, seating, spectrum, slot, blending, discrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ipad, gbg, fidelity, app, 2014, id, tau, 2010, 2011, 2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">covid, pandemic, nick, 2020, asynchronous, compassion, 2021, hallucinations, emt, 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25th pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50th pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75th pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 10 reused words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">behavior, subjects, children, training, design, treatment, generalization, baseline, behavioral, self</t>
-  </si>
-  <si>
-    <t xml:space="preserve">behavior, study, design, treatment, results, children, self, training, social, effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">children, study, design, behavior, treatment, results, video, participants, training, effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention, study, design, children, participants, results, students, video, based, training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention, study, design, participants, children, training, students, skills, asd, based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 10 new words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">behavior, children, self, training, baseline, assessment, design, sensory, treatment, use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">performance, community, treatments, coaching, restraint, cognitive, conditions, improvement, casts, handicapped</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autism, matching, delay, developmental, object, participant, injury, spelling, second, output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">symbol, pecs, asd, stories, knee, protocol, seating, spectrum, slot, blending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ipad, 2016, tablet, gbg, fidelity, app, 2014, scribe, id, tau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">covid, pandemic, nick, 2020, asynchronous, compassion, 2021, hallucinations, emt, 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25th pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50th pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75th pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Max</t>
   </si>
   <si>
-    <t xml:space="preserve">39</t>
+    <t xml:space="preserve">40</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
@@ -231,52 +234,52 @@
     <t xml:space="preserve">433</t>
   </si>
   <si>
-    <t xml:space="preserve">1510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2422</t>
+    <t xml:space="preserve">1519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2425</t>
   </si>
   <si>
     <t xml:space="preserve">Skew</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.33</t>
+    <t xml:space="preserve">5.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55</t>
   </si>
   <si>
     <t xml:space="preserve">Kurt</t>
   </si>
   <si>
-    <t xml:space="preserve">56.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.4</t>
+    <t xml:space="preserve">48.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.06</t>
   </si>
   <si>
     <t xml:space="preserve">Decade</t>
@@ -292,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
   </si>
   <si>
     <t xml:space="preserve">13</t>
@@ -929,79 +929,79 @@
         <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1020,16 +1020,16 @@
         <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -1040,10 +1040,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="D2" t="n">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>798</v>
+        <v>633</v>
       </c>
       <c r="D3" t="n">
-        <v>377</v>
+        <v>294</v>
       </c>
       <c r="E3" t="n">
-        <v>421</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4">
@@ -1074,13 +1074,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4209</v>
+        <v>3235</v>
       </c>
       <c r="D4" t="n">
-        <v>1785</v>
+        <v>1233</v>
       </c>
       <c r="E4" t="n">
-        <v>2424</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="5">
@@ -1091,13 +1091,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8327</v>
+        <v>8113</v>
       </c>
       <c r="D5" t="n">
-        <v>1490</v>
+        <v>1413</v>
       </c>
       <c r="E5" t="n">
-        <v>6837</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="6">
@@ -1108,13 +1108,13 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26785</v>
+        <v>25059</v>
       </c>
       <c r="D6" t="n">
-        <v>3211</v>
+        <v>3092</v>
       </c>
       <c r="E6" t="n">
-        <v>23574</v>
+        <v>21967</v>
       </c>
     </row>
     <row r="7">
@@ -1125,183 +1125,183 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47760</v>
+        <v>44394</v>
       </c>
       <c r="D7" t="n">
-        <v>3495</v>
+        <v>3203</v>
       </c>
       <c r="E7" t="n">
-        <v>44265</v>
+        <v>41191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>171</v>
+        <v>731</v>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>319</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>463</v>
+        <v>2122</v>
       </c>
       <c r="D9" t="n">
-        <v>171</v>
+        <v>822</v>
       </c>
       <c r="E9" t="n">
-        <v>292</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1093</v>
+        <v>3560</v>
       </c>
       <c r="D10" t="n">
-        <v>143</v>
+        <v>532</v>
       </c>
       <c r="E10" t="n">
-        <v>950</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>4872</v>
+        <v>7625</v>
       </c>
       <c r="D11" t="n">
-        <v>407</v>
+        <v>730</v>
       </c>
       <c r="E11" t="n">
-        <v>4465</v>
+        <v>6895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>11746</v>
+        <v>8051</v>
       </c>
       <c r="D12" t="n">
-        <v>396</v>
+        <v>577</v>
       </c>
       <c r="E12" t="n">
-        <v>11350</v>
+        <v>7474</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="E14" t="n">
-        <v>260</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>1785</v>
+        <v>810</v>
       </c>
       <c r="D15" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>1659</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>12091</v>
+        <v>4101</v>
       </c>
       <c r="D16" t="n">
-        <v>758</v>
+        <v>349</v>
       </c>
       <c r="E16" t="n">
-        <v>11333</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>557</v>
+        <v>9199</v>
       </c>
       <c r="D17" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="E17" t="n">
-        <v>327</v>
+        <v>8951</v>
       </c>
     </row>
     <row r="18">
@@ -1309,16 +1309,16 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>914</v>
+        <v>195</v>
       </c>
       <c r="D18" t="n">
-        <v>266</v>
+        <v>195</v>
       </c>
       <c r="E18" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1326,16 +1326,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>2863</v>
+        <v>408</v>
       </c>
       <c r="D19" t="n">
-        <v>409</v>
+        <v>127</v>
       </c>
       <c r="E19" t="n">
-        <v>2454</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20">
@@ -1343,16 +1343,16 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>5175</v>
+        <v>973</v>
       </c>
       <c r="D20" t="n">
-        <v>432</v>
+        <v>190</v>
       </c>
       <c r="E20" t="n">
-        <v>4743</v>
+        <v>783</v>
       </c>
     </row>
     <row r="21">
@@ -1360,50 +1360,50 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>6179</v>
+        <v>1332</v>
       </c>
       <c r="D21" t="n">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>5837</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>5123</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>4874</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>6368</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="24">
@@ -1411,16 +1411,16 @@
         <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>445</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1428,16 +1428,16 @@
         <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>478</v>
+        <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>435</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1445,16 +1445,16 @@
         <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>4687</v>
+        <v>445</v>
       </c>
       <c r="D26" t="n">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="E26" t="n">
-        <v>4282</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27">
@@ -1462,50 +1462,50 @@
         <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4185</v>
+        <v>340</v>
       </c>
       <c r="D27" t="n">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
-        <v>4039</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>141</v>
+        <v>4610</v>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>390</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>415</v>
+        <v>4201</v>
       </c>
       <c r="D29" t="n">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="E29" t="n">
-        <v>364</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="30">
@@ -1513,16 +1513,16 @@
         <v>95</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3905</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>363</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>3542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1530,67 +1530,67 @@
         <v>95</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>5060</v>
+        <v>957</v>
       </c>
       <c r="D31" t="n">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="E31" t="n">
-        <v>4807</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>985</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>860</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>614</v>
+        <v>2653</v>
       </c>
       <c r="D33" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E33" t="n">
-        <v>409</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>1158</v>
+        <v>3118</v>
       </c>
       <c r="D34" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="E34" t="n">
-        <v>1015</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="35">
@@ -1598,16 +1598,16 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>2493</v>
+        <v>192</v>
       </c>
       <c r="D35" t="n">
-        <v>206</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>2287</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36">
@@ -1615,50 +1615,50 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>1513</v>
+        <v>796</v>
       </c>
       <c r="D36" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="E36" t="n">
-        <v>1430</v>
+        <v>685</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>922</v>
+        <v>4650</v>
       </c>
       <c r="D37" t="n">
-        <v>922</v>
+        <v>412</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>1252</v>
+        <v>4399</v>
       </c>
       <c r="D38" t="n">
-        <v>538</v>
+        <v>210</v>
       </c>
       <c r="E38" t="n">
-        <v>714</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="39">
@@ -1666,16 +1666,16 @@
         <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>4524</v>
+        <v>69</v>
       </c>
       <c r="D39" t="n">
-        <v>1135</v>
+        <v>69</v>
       </c>
       <c r="E39" t="n">
-        <v>3389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1683,16 +1683,16 @@
         <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>7267</v>
+        <v>318</v>
       </c>
       <c r="D40" t="n">
-        <v>763</v>
+        <v>137</v>
       </c>
       <c r="E40" t="n">
-        <v>6504</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
@@ -1700,16 +1700,16 @@
         <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>18828</v>
+        <v>1819</v>
       </c>
       <c r="D41" t="n">
-        <v>1471</v>
+        <v>430</v>
       </c>
       <c r="E41" t="n">
-        <v>17357</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="42">
@@ -1717,50 +1717,50 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>16145</v>
+        <v>4790</v>
       </c>
       <c r="D42" t="n">
-        <v>730</v>
+        <v>383</v>
       </c>
       <c r="E42" t="n">
-        <v>15415</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>69</v>
+        <v>24600</v>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>1418</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>23182</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>173</v>
+        <v>21893</v>
       </c>
       <c r="D44" t="n">
-        <v>75</v>
+        <v>676</v>
       </c>
       <c r="E44" t="n">
-        <v>98</v>
+        <v>21217</v>
       </c>
     </row>
     <row r="45">
@@ -1768,16 +1768,16 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>1634</v>
+        <v>68</v>
       </c>
       <c r="D45" t="n">
-        <v>392</v>
+        <v>68</v>
       </c>
       <c r="E45" t="n">
-        <v>1242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1785,16 +1785,16 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>4277</v>
+        <v>248</v>
       </c>
       <c r="D46" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="E46" t="n">
-        <v>3944</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47">
@@ -1802,16 +1802,16 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>18946</v>
+        <v>1187</v>
       </c>
       <c r="D47" t="n">
-        <v>1057</v>
+        <v>332</v>
       </c>
       <c r="E47" t="n">
-        <v>17889</v>
+        <v>855</v>
       </c>
     </row>
     <row r="48">
@@ -1819,50 +1819,50 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>15683</v>
+        <v>1944</v>
       </c>
       <c r="D48" t="n">
-        <v>450</v>
+        <v>226</v>
       </c>
       <c r="E48" t="n">
-        <v>15233</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>100</v>
+        <v>13346</v>
       </c>
       <c r="D49" t="n">
-        <v>100</v>
+        <v>1235</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>12111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>144</v>
+        <v>51156</v>
       </c>
       <c r="D50" t="n">
-        <v>75</v>
+        <v>3184</v>
       </c>
       <c r="E50" t="n">
-        <v>69</v>
+        <v>47972</v>
       </c>
     </row>
     <row r="51">
@@ -1870,16 +1870,16 @@
         <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1262</v>
+        <v>1135</v>
       </c>
       <c r="D51" t="n">
-        <v>419</v>
+        <v>1135</v>
       </c>
       <c r="E51" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1887,16 +1887,16 @@
         <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>1645</v>
+        <v>1325</v>
       </c>
       <c r="D52" t="n">
-        <v>187</v>
+        <v>543</v>
       </c>
       <c r="E52" t="n">
-        <v>1458</v>
+        <v>782</v>
       </c>
     </row>
     <row r="53">
@@ -1904,16 +1904,16 @@
         <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>9980</v>
+        <v>4393</v>
       </c>
       <c r="D53" t="n">
-        <v>979</v>
+        <v>1176</v>
       </c>
       <c r="E53" t="n">
-        <v>9001</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="54">
@@ -1921,50 +1921,50 @@
         <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>32079</v>
+        <v>7006</v>
       </c>
       <c r="D54" t="n">
-        <v>2174</v>
+        <v>836</v>
       </c>
       <c r="E54" t="n">
-        <v>29905</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C55" t="n">
-        <v>246</v>
+        <v>12858</v>
       </c>
       <c r="D55" t="n">
-        <v>246</v>
+        <v>1092</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>11766</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>108</v>
+        <v>9451</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>540</v>
       </c>
       <c r="E56" t="n">
-        <v>67</v>
+        <v>8911</v>
       </c>
     </row>
     <row r="57">
@@ -1972,16 +1972,16 @@
         <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>1126</v>
+        <v>198</v>
       </c>
       <c r="D57" t="n">
-        <v>398</v>
+        <v>198</v>
       </c>
       <c r="E57" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1989,16 +1989,16 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>2231</v>
+        <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>441</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>1790</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -2006,16 +2006,16 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>14582</v>
+        <v>1528</v>
       </c>
       <c r="D59" t="n">
-        <v>1853</v>
+        <v>555</v>
       </c>
       <c r="E59" t="n">
-        <v>12729</v>
+        <v>973</v>
       </c>
     </row>
     <row r="60">
@@ -2023,50 +2023,50 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>19865</v>
+        <v>2704</v>
       </c>
       <c r="D60" t="n">
-        <v>1275</v>
+        <v>479</v>
       </c>
       <c r="E60" t="n">
-        <v>18590</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>106</v>
+        <v>15628</v>
       </c>
       <c r="D61" t="n">
-        <v>106</v>
+        <v>2054</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>13574</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>774</v>
+        <v>21156</v>
       </c>
       <c r="D62" t="n">
-        <v>225</v>
+        <v>1506</v>
       </c>
       <c r="E62" t="n">
-        <v>549</v>
+        <v>19650</v>
       </c>
     </row>
     <row r="63">
@@ -2074,16 +2074,16 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>3640</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>473</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>3167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2091,16 +2091,16 @@
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>11447</v>
+        <v>952</v>
       </c>
       <c r="D64" t="n">
-        <v>691</v>
+        <v>273</v>
       </c>
       <c r="E64" t="n">
-        <v>10756</v>
+        <v>679</v>
       </c>
     </row>
     <row r="65">
@@ -2108,50 +2108,50 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>14641</v>
+        <v>3748</v>
       </c>
       <c r="D65" t="n">
-        <v>422</v>
+        <v>476</v>
       </c>
       <c r="E65" t="n">
-        <v>14219</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>11544</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>678</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>1218</v>
+        <v>14375</v>
       </c>
       <c r="D67" t="n">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="E67" t="n">
-        <v>758</v>
+        <v>13967</v>
       </c>
     </row>
     <row r="68">
@@ -2159,16 +2159,16 @@
         <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>2832</v>
+        <v>57</v>
       </c>
       <c r="D68" t="n">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="E68" t="n">
-        <v>2498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2176,16 +2176,16 @@
         <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>9488</v>
+        <v>674</v>
       </c>
       <c r="D69" t="n">
-        <v>692</v>
+        <v>289</v>
       </c>
       <c r="E69" t="n">
-        <v>8796</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70">
@@ -2193,67 +2193,67 @@
         <v>97</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>13152</v>
+        <v>1771</v>
       </c>
       <c r="D70" t="n">
-        <v>492</v>
+        <v>587</v>
       </c>
       <c r="E70" t="n">
-        <v>12660</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>195</v>
+        <v>2736</v>
       </c>
       <c r="D71" t="n">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B72" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>397</v>
+        <v>7448</v>
       </c>
       <c r="D72" t="n">
-        <v>131</v>
+        <v>488</v>
       </c>
       <c r="E72" t="n">
-        <v>266</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B73" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>1624</v>
+        <v>10719</v>
       </c>
       <c r="D73" t="n">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="E73" t="n">
-        <v>1265</v>
+        <v>10323</v>
       </c>
     </row>
     <row r="74">
@@ -2261,16 +2261,16 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>1688</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>1535</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -2278,16 +2278,16 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>10127</v>
+        <v>1049</v>
       </c>
       <c r="D75" t="n">
-        <v>728</v>
+        <v>403</v>
       </c>
       <c r="E75" t="n">
-        <v>9399</v>
+        <v>646</v>
       </c>
     </row>
     <row r="76">
@@ -2295,118 +2295,152 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>12375</v>
+        <v>2535</v>
       </c>
       <c r="D76" t="n">
-        <v>475</v>
+        <v>280</v>
       </c>
       <c r="E76" t="n">
-        <v>11900</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C77" t="n">
-        <v>68</v>
+        <v>8499</v>
       </c>
       <c r="D77" t="n">
-        <v>68</v>
+        <v>597</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C78" t="n">
-        <v>746</v>
+        <v>13107</v>
       </c>
       <c r="D78" t="n">
-        <v>307</v>
+        <v>467</v>
       </c>
       <c r="E78" t="n">
-        <v>439</v>
+        <v>12640</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1813</v>
+        <v>40</v>
       </c>
       <c r="D79" t="n">
-        <v>579</v>
+        <v>40</v>
       </c>
       <c r="E79" t="n">
-        <v>1234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>2544</v>
+        <v>27</v>
       </c>
       <c r="D80" t="n">
-        <v>275</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>2269</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>6656</v>
+        <v>612</v>
       </c>
       <c r="D81" t="n">
-        <v>458</v>
+        <v>163</v>
       </c>
       <c r="E81" t="n">
-        <v>6198</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1470</v>
+      </c>
+      <c r="D82" t="n">
+        <v>154</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" t="n">
+        <v>6345</v>
+      </c>
+      <c r="D83" t="n">
+        <v>480</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5865</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" t="s">
         <v>6</v>
       </c>
-      <c r="C82" t="n">
-        <v>10586</v>
-      </c>
-      <c r="D82" t="n">
-        <v>341</v>
-      </c>
-      <c r="E82" t="n">
-        <v>10245</v>
+      <c r="C84" t="n">
+        <v>7055</v>
+      </c>
+      <c r="D84" t="n">
+        <v>211</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6844</v>
       </c>
     </row>
   </sheetData>
